--- a/TaskyRevamp/TaskyRevamp/wwwroot/إضافة إدارات.xlsx
+++ b/TaskyRevamp/TaskyRevamp/wwwroot/إضافة إدارات.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\source\repos\TaskyRevamp\TaskyRevamp\TaskyRevamp\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BF440AB-B439-4BA5-AE7A-4E6A2A1929ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA16505-E1B0-4ED0-BE5C-61758A7B8BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1B11774-1335-484B-BDD7-E8A04FD97A9C}"/>
   </bookViews>
@@ -34,15 +34,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>مستوى الإدارة</t>
   </si>
   <si>
-    <t>اسم الإدارة</t>
+    <t xml:space="preserve">الإدارة الرئيسية </t>
   </si>
   <si>
-    <t xml:space="preserve">الإدارة الرئيسية </t>
+    <t>اسم الإدارة بالانجليزية</t>
+  </si>
+  <si>
+    <t>اسم الإدارة بالعربية</t>
   </si>
 </sst>
 </file>
@@ -394,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B12B9828-2B6F-4D7D-86AF-271D87043B03}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -402,15 +405,18 @@
     <col min="3" max="3" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
